--- a/01_用AI生成Excel/10_髒資料清洗/採購需求清洗.xlsx
+++ b/01_用AI生成Excel/10_髒資料清洗/採購需求清洗.xlsx
@@ -162,7 +162,9 @@
     <tableColumn id="6" name="數量"/>
     <tableColumn id="7" name="單位"/>
     <tableColumn id="8" name="單價"/>
-    <tableColumn id="9" name="小計"/>
+    <tableColumn id="9" name="小計">
+      <calculatedColumnFormula>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -682,7 +684,7 @@
         <v>6500</v>
       </c>
       <c r="I2" s="4">
-        <f>F2*H2</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -720,7 +722,7 @@
         <v>135</v>
       </c>
       <c r="I3" s="4">
-        <f>F3*H3</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -758,7 +760,7 @@
         <v>450</v>
       </c>
       <c r="I4" s="4">
-        <f>F4*H4</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -796,7 +798,7 @@
         <v>160</v>
       </c>
       <c r="I5" s="4">
-        <f>F5*H5</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -834,7 +836,7 @@
         <v>2490</v>
       </c>
       <c r="I6" s="4">
-        <f>F6*H6</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -872,7 +874,7 @@
         <v>350</v>
       </c>
       <c r="I7" s="4">
-        <f>F7*H7</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -910,7 +912,7 @@
         <v>1800</v>
       </c>
       <c r="I8" s="4">
-        <f>F8*H8</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -948,7 +950,7 @@
         <v>4200</v>
       </c>
       <c r="I9" s="4">
-        <f>F9*H9</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -986,7 +988,7 @@
         <v>1150</v>
       </c>
       <c r="I10" s="4">
-        <f>F10*H10</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
@@ -1024,7 +1026,7 @@
         <v>1290</v>
       </c>
       <c r="I11" s="4">
-        <f>F11*H11</f>
+        <f>T_Purchase[[#This Row],[數量]]*T_Purchase[[#This Row],[單價]]</f>
         <v/>
       </c>
     </row>
